--- a/sheets/조재수대금교본/검수/그 저녁 무렵부터 새벽이 오기까지.xlsx
+++ b/sheets/조재수대금교본/검수/그 저녁 무렵부터 새벽이 오기까지.xlsx
@@ -2592,11 +2592,7 @@
     </row>
     <row r="5" ht="86.26" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
@@ -2659,7 +2655,7 @@
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㄴ</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -2671,7 +2667,7 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㄴ</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -2683,7 +2679,7 @@
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㄴ</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -2696,85 +2692,64 @@
       <c r="E7" s="23"/>
       <c r="F7" s="21"/>
       <c r="G7" s="23"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H7" s="21"/>
       <c r="I7" s="23"/>
       <c r="J7" s="21"/>
       <c r="K7" s="23"/>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L7" s="21"/>
       <c r="M7" s="23"/>
       <c r="N7" s="21"/>
       <c r="O7" s="23"/>
-      <c r="P7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P7" s="21"/>
       <c r="Q7" s="23"/>
     </row>
     <row r="8" ht="86.26" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲∼
-‹</t>
+          <t xml:space="preserve">仲∼</t>
         </is>
       </c>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄴ
-ﾉ
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲∼
-‹</t>
+          <t xml:space="preserve">仲∼</t>
         </is>
       </c>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲∼
-‹</t>
+          <t xml:space="preserve">仲∼</t>
         </is>
       </c>
       <c r="Q8" s="24"/>
@@ -2856,15 +2831,13 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-ﾉ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -2885,7 +2858,7 @@
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㶐ㅂ</t>
+          <t xml:space="preserve">㶐</t>
         </is>
       </c>
       <c r="E12" s="22"/>
@@ -2936,16 +2909,11 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/그 저녁 무렵부터 새벽이 오기까지.xlsx
+++ b/sheets/조재수대금교본/검수/그 저녁 무렵부터 새벽이 오기까지.xlsx
@@ -2655,7 +2655,7 @@
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太ㄴ</t>
         </is>
       </c>
       <c r="I6" s="22"/>
@@ -2667,7 +2667,7 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太ㄴ</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -2679,7 +2679,7 @@
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太ㄴ</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
@@ -2731,7 +2731,8 @@
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄴ
+ﾉ</t>
         </is>
       </c>
       <c r="K8" s="24"/>
@@ -2837,7 +2838,8 @@
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+ﾉ</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -2858,7 +2860,7 @@
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㶐</t>
+          <t xml:space="preserve">㶐ㅂ</t>
         </is>
       </c>
       <c r="E12" s="22"/>

--- a/sheets/조재수대금교본/검수/그 저녁 무렵부터 새벽이 오기까지.xlsx
+++ b/sheets/조재수대금교본/검수/그 저녁 무렵부터 새벽이 오기까지.xlsx
@@ -2476,28 +2476,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="57.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="86.26" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="86.26" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -2590,7 +2590,7 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="86.26" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="86.26" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="86.26" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -2703,7 +2703,7 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="86.26" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="86.26" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="86.26" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -2826,7 +2826,7 @@
       <c r="P10" s="21"/>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="86.26" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -2854,7 +2854,7 @@
       <c r="P11" s="21"/>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="86.26" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -2881,7 +2881,7 @@
       <c r="P12" s="21"/>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="86.26" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -2900,7 +2900,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="86.26" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2959,6 +2959,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="69"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>